--- a/outputs/gr_SSP2_population_baseyear.xlsx
+++ b/outputs/gr_SSP2_population_baseyear.xlsx
@@ -1,171 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2030</t>
-  </si>
-  <si>
-    <t>2035</t>
-  </si>
-  <si>
-    <t>2040</t>
-  </si>
-  <si>
-    <t>2045</t>
-  </si>
-  <si>
-    <t>2050</t>
-  </si>
-  <si>
-    <t>2060</t>
-  </si>
-  <si>
-    <t>2070</t>
-  </si>
-  <si>
-    <t>2080</t>
-  </si>
-  <si>
-    <t>2090</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>OMNIA</t>
-  </si>
-  <si>
-    <t>AFE</t>
-  </si>
-  <si>
-    <t>AFN</t>
-  </si>
-  <si>
-    <t>AFW</t>
-  </si>
-  <si>
-    <t>AFZ</t>
-  </si>
-  <si>
-    <t>ANZ</t>
-  </si>
-  <si>
-    <t>ASC</t>
-  </si>
-  <si>
-    <t>ASE</t>
-  </si>
-  <si>
-    <t>ASO</t>
-  </si>
-  <si>
-    <t>BRA</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>CHL</t>
-  </si>
-  <si>
-    <t>CHN</t>
-  </si>
-  <si>
-    <t>ENE</t>
-  </si>
-  <si>
-    <t>ENW</t>
-  </si>
-  <si>
-    <t>EUE</t>
-  </si>
-  <si>
-    <t>EUM</t>
-  </si>
-  <si>
-    <t>EUW</t>
-  </si>
-  <si>
-    <t>IDN</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>JPN</t>
-  </si>
-  <si>
-    <t>LAM</t>
-  </si>
-  <si>
-    <t>MDA</t>
-  </si>
-  <si>
-    <t>MEA</t>
-  </si>
-  <si>
-    <t>MEX</t>
-  </si>
-  <si>
-    <t>NIG</t>
-  </si>
-  <si>
-    <t>RUS</t>
-  </si>
-  <si>
-    <t>SKT</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -180,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -496,1287 +420,1375 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OMNIA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AFE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
         <v>1.107797808597177</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1.162448106854038</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1.306327363546583</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1.45314355497303</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1.599734161116514</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1.744277338417613</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1.88489827147096</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>2.141437802561281</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>2.351992751101367</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>2.50526459370183</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>2.602367689042827</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>2.6516782807709</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AFN</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>1.064367414750556</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>1.096089254264352</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1.171538107362818</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>1.243652888413775</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1.313726821274166</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>1.379746125772065</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>1.439199765405608</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>1.532207780687216</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>1.589593464400542</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>1.623402203972888</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>1.639937129803584</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>1.636729174966703</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AFW</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>1.119592330761573</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>1.180819902448421</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1.345949976691015</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1.519630349631431</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1.699267178659714</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1.88158081655024</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>2.062980741783429</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>2.408409944911229</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>2.714819601576247</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>2.964435117044469</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>3.144675074409804</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>3.252378650898963</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AFZ</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
         <v>1.084615121667852</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1.12646733065527</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1.235028111941247</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1.342699125179956</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1.44781357422487</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>1.548183108790351</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>1.641168207791429</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>1.8017826416252</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>1.922080082202477</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>1.996333444426597</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>2.024163293767027</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>2.01625622420273</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
         <v>1.039240942573019</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>1.054869718192087</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1.092340772326107</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>1.127081858971791</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>1.159807377050733</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>1.191907247813642</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>1.224239979397134</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>1.281549725444533</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1.325794776608819</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1.355961218067041</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>1.366631712954965</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>1.360596902827478</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
         <v>1.052671840463655</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>1.078549769967068</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1.136445765048792</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1.189186946671498</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.239667876309047</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>1.287068740897279</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>1.328521399559715</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>1.384404287120593</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>1.413014287120915</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>1.426347835318825</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>1.427802764689607</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>1.41935456352404</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ASE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>1.029751319985705</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1.043496908606694</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1.070407250422949</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1.089517661453317</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1.101237814784312</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>1.106381096005818</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>1.105853747762477</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>1.090063924613808</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>1.058466467211014</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>1.016582284001077</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>0.9675673580509816</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>0.9144919945642022</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ASO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
         <v>1.060122099701225</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>1.092000604062304</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1.170892774550798</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1.245767788925932</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1.315220028522022</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>1.378624733607588</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>1.436628868260484</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>1.533062511187397</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>1.59899924216575</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>1.633090879841961</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>1.642402364251239</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>1.635994534091543</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
         <v>1.022019046785109</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>1.031495699102609</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1.053583414931358</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1.069619217323444</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1.079295300784985</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1.082796390334507</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>1.080099306447969</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>1.059779246235104</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>1.022489598234814</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>0.9724828829527001</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>0.9170685207838195</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>0.8629438438162551</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.026001427388915</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>1.035490125215188</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1.056913365471628</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1.076819069826727</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>1.094960795787863</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>1.112166699457783</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>1.130013884168631</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>1.159564742632042</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>1.185028975227537</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>1.201703595293977</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>1.201522856508206</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>1.18680605684852</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
         <v>1.026960738017386</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>1.03487410120858</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1.054369313304102</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.069016725011755</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>1.07788859187513</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>1.08121132709072</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>1.080208640077675</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>1.063973059239617</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>1.031337848412729</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>0.9857773191542298</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>0.9297730848257885</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>0.871111772193485</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
         <v>1.00585058740407</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>1.006534078592001</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>0.9994752821269225</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>0.9872581504549859</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>0.9710022215691222</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>0.9496722840324535</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>0.9220918866182209</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>0.8498928504499749</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>0.7714780581602347</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>0.6976041249748709</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>0.6277269295637504</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>0.5662625390943787</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
         <v>0.9264904467300136</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>0.8803291004898658</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>0.8794747915475569</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>0.870625191428032</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>0.8559728264206673</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>0.8379706120118356</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>0.8190739670377289</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>0.7804918906077691</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>0.7426480438772789</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>0.7071843386212082</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>0.6747441493490232</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>0.6432847426058161</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ENW</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.015853774986522</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1.022215258234717</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1.036700509321928</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1.05112475523158</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>1.066444952790114</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>1.083340465459205</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>1.101749272958912</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>1.12963762647235</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>1.151418690754416</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>1.170907629089629</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>1.178584031403564</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>1.17694280891368</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EUE</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
         <v>0.9944548771294623</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>0.9923837920039558</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>0.969089417879291</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>0.9450401110752604</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>0.9218129821112365</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>0.899933495726734</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>0.8797679333207247</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>0.8392773057367116</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>0.7955441004382161</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>0.7534560929572011</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>0.7190199884850962</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>0.6909152573968868</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EUM</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
         <v>1.000697201008509</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>1.000670449029756</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>1.000099565805853</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1.00087140867271</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>1.002878369312276</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1.005107231487773</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1.007162502908035</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1.002470672952443</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>0.9903684097399915</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>0.980924229821343</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>0.9735874645732293</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>0.9594621010209352</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EUW</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.010293442952702</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>1.014070752965147</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>1.014983413073265</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>1.015472075664274</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>1.016174233921906</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>1.017447736927984</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>1.019111201419298</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>1.018974115797571</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>1.016866557290326</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>1.013343763644258</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>1.00105739960368</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>0.982784256729298</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.039156097624212</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>1.057708557899352</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>1.102385774662812</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>1.140225074132666</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>1.170735304478436</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>1.194123622904948</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>1.210484363039995</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="n">
         <v>1.224900159263986</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>1.218853628712395</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>1.196975546927328</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="n">
         <v>1.161789494913839</v>
       </c>
-      <c r="N19">
+      <c r="N19" t="n">
         <v>1.118538900894461</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
         <v>1.035113340040058</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>1.051262699002796</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>1.092168951225106</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1.125872453941703</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>1.151777642957666</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>1.16923784984293</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>1.178447565674224</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>1.180057565809605</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>1.159769559730946</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>1.11963644706609</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>1.067831316331034</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>1.012083182725731</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.9824710324785619</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>0.972717873699768</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>0.9478983953938181</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>0.9217115435408961</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>0.8948270224610606</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>0.8678014616720706</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>0.8417404796981146</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>0.7921163434543464</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>0.7382767099592229</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>0.6842173839652295</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>0.6386590401931213</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>0.5959988011418221</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
         <v>1.034588475393715</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>1.051277626081208</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>1.093065000610318</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1.129306359544592</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1.158975567855367</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>1.181915773459077</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>1.198422040019471</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>1.214151224945974</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>1.210950272977344</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>1.191592506525984</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>1.15956555960293</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>1.120539086277984</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
         <v>1.041454540456636</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>1.06105455272508</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>1.106689144973814</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1.146754019401692</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>1.182084155084046</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>1.212155963247388</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>1.234935602870136</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>1.258998376644555</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>1.260759820783128</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>1.248953068482927</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>1.226177699567956</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>1.19619513991301</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>MEA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
         <v>1.06684649416495</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>1.098599074295586</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>1.175347221177368</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1.246726569523813</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>1.313302474677251</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>1.374249753008496</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>1.42767276339954</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>1.506838619028207</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>1.542497174361585</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>1.544678196314524</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>1.529791534968381</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>1.503430564736898</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.033024408116105</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>1.048460821423427</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>1.090331897396149</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>1.12736980635297</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>1.158517963569953</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>1.183095197869583</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>1.201274306411152</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>1.222636153231559</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>1.2268107325725</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>1.216720537793705</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>1.197024459447948</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>1.171679579014055</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>NIG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
         <v>1.102671641068873</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>1.15514452221649</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1.299410306009476</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1.457275362482226</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>1.627885751945831</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>1.807765749982623</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>1.993362464513612</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>2.360941956044625</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>2.710030049698368</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>3.025802155028058</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>3.284909769980349</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>3.466920521999203</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
         <v>1.000201106957144</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>0.9991257222706886</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>0.9855807316554623</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>0.9729893712259016</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>0.9635213522349158</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>0.9576236301970885</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>0.9536674233672807</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>0.9411991164281032</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>0.9222028163257292</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>0.9025327186371619</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>0.883475998336287</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>0.8609899455085137</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
         <v>0.9983771961197313</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>0.9948125734762182</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>0.9825081439152729</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>0.9657594910993844</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>0.9428092657975443</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>0.9144699564694624</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>0.8833099812992072</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>0.8042864574287157</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>0.7217136893456185</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>0.6471439007512578</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>0.5823934631671072</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>0.5253335942112382</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
         <v>1.019165065485943</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>1.027120834210988</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>1.0502378702155</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>1.072904825563894</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>1.094253156428303</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>1.113864204430245</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>1.132274550833962</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>1.163288732278765</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>1.192270168953349</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>1.214067406230299</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>1.221229027716888</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>1.217797704788065</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/gr_SSP2_population_baseyear.xlsx
+++ b/outputs/gr_SSP2_population_baseyear.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,79 +417,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OMNIA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2045</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2070</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2080</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2090</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>AFE</t>
         </is>
@@ -547,7 +535,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>AFN</t>
         </is>
@@ -593,7 +581,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>AFW</t>
         </is>
@@ -639,7 +627,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>AFZ</t>
         </is>
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>ANZ</t>
         </is>
@@ -731,7 +719,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>ASC</t>
         </is>
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ASE</t>
         </is>
@@ -823,7 +811,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>ASO</t>
         </is>
@@ -869,7 +857,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>BRA</t>
         </is>
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
@@ -961,7 +949,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CHL</t>
         </is>
@@ -1007,7 +995,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CHN</t>
         </is>
@@ -1053,7 +1041,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ENE</t>
         </is>
@@ -1099,7 +1087,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ENW</t>
         </is>
@@ -1145,7 +1133,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>EUE</t>
         </is>
@@ -1191,7 +1179,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>EUM</t>
         </is>
@@ -1237,7 +1225,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>EUW</t>
         </is>
@@ -1283,7 +1271,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>IDN</t>
         </is>
@@ -1329,7 +1317,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
@@ -1375,7 +1363,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>JPN</t>
         </is>
@@ -1421,7 +1409,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>LAM</t>
         </is>
@@ -1467,7 +1455,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>MDA</t>
         </is>
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>MEA</t>
         </is>
@@ -1559,7 +1547,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>MEX</t>
         </is>
@@ -1605,7 +1593,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>NIG</t>
         </is>
@@ -1651,7 +1639,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>RUS</t>
         </is>
@@ -1697,7 +1685,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>SKT</t>
         </is>
@@ -1743,7 +1731,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
